--- a/Trắc nghiệm ôn luyện/DA Engineering/multiple_choice_sample_template_SQL_QUERIES.xlsx
+++ b/Trắc nghiệm ôn luyện/DA Engineering/multiple_choice_sample_template_SQL_QUERIES.xlsx
@@ -453,19 +453,19 @@
         <v>WHERE dùng để lọc các dòng dữ liệu (rows) thỏa mãn điều kiện lọc cụ thể từ bảng dữ liệu nguồn.</v>
       </c>
       <c r="E2" t="str">
+        <v>Tính tổng giá trị của một cột số trong bảng cơ sở dữ liệu — gom nhóm dữ liệu</v>
+      </c>
+      <c r="F2" t="str">
         <v>Lọc các bản ghi thỏa mãn điều kiện chỉ định trước khi trả về kết quả — lọc dữ liệu theo hàng</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Sắp xếp thứ tự các cột hiển thị trong bảng kết quả theo thứ tự bảng chữ cái — sắp xếp cột</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Cập nhật giá trị mới cho các cột trong bảng cơ sở dữ liệu — thay đổi dữ liệu bảng</v>
       </c>
-      <c r="H2" t="str">
-        <v>Tính tổng giá trị của một cột số trong bảng cơ sở dữ liệu — gom nhóm dữ liệu</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>INNER JOIN chỉ trả về các bản ghi khớp giá trị ở cả hai bảng. LEFT JOIN trả về toàn bộ bản ghi bảng bên trái (Left), nếu bảng bên phải không có dòng khớp thì hiển thị NULL.</v>
       </c>
       <c r="E3" t="str">
+        <v>INNER JOIN chạy nhanh hơn LEFT JOIN gấp 10 lần trong mọi trường hợp cơ sở dữ liệu</v>
+      </c>
+      <c r="F3" t="str">
+        <v>INNER JOIN gộp hai bảng theo chiều dọc; LEFT JOIN gộp hai bảng theo chiều ngang</v>
+      </c>
+      <c r="G3" t="str">
+        <v>INNER JOIN lấy tất cả dòng bảng bên phải; LEFT JOIN chỉ lấy dòng khớp nhau ở cả hai bảng</v>
+      </c>
+      <c r="H3" t="str">
         <v>INNER JOIN chỉ lấy các dòng khớp nhau ở cả hai bảng; LEFT JOIN lấy tất cả dòng bảng bên trái và dòng khớp ở bảng bên phải</v>
       </c>
-      <c r="F3" t="str">
-        <v>INNER JOIN lấy tất cả dòng bảng bên phải; LEFT JOIN chỉ lấy dòng khớp nhau ở cả hai bảng</v>
-      </c>
-      <c r="G3" t="str">
-        <v>INNER JOIN gộp hai bảng theo chiều dọc; LEFT JOIN gộp hai bảng theo chiều ngang</v>
-      </c>
-      <c r="H3" t="str">
-        <v>INNER JOIN chạy nhanh hơn LEFT JOIN gấp 10 lần trong mọi trường hợp cơ sở dữ liệu</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>ORDER BY dùng để sắp xếp kết quả (mặc định ASC tăng dần, DESC giảm dần) và là mệnh đề đứng cuối cùng trong câu lệnh SELECT.</v>
       </c>
       <c r="E4" t="str">
+        <v>Đặt bí danh cho các cột hiển thị trong kết quả; đứng ngay sau tên bảng ở FROM</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Gom nhóm các bản ghi có cùng giá trị; đứng trước mệnh đề GROUP BY</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Lọc các bản ghi trùng lặp trong kết quả trả về; đứng ngay sau mệnh đề FROM</v>
+      </c>
+      <c r="H4" t="str">
         <v>Sắp xếp kết quả trả về theo thứ tự tăng/giảm dần; luôn đứng ở cuối câu lệnh SELECT</v>
       </c>
-      <c r="F4" t="str">
-        <v>Lọc các bản ghi trùng lặp trong kết quả trả về; đứng ngay sau mệnh đề FROM</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Gom nhóm các bản ghi có cùng giá trị; đứng trước mệnh đề GROUP BY</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Đặt bí danh cho các cột hiển thị trong kết quả; đứng ngay sau tên bảng ở FROM</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>COUNT() là hàm gom nhóm dùng để đếm số lượng dòng dữ liệu (ví dụ: COUNT(*) đếm toàn bộ dòng, COUNT(column) đếm dòng có giá trị khác NULL).</v>
       </c>
       <c r="E5" t="str">
+        <v>TOTAL() — hàm tính tổng số cột hiển thị trong bảng</v>
+      </c>
+      <c r="F5" t="str">
         <v>COUNT() — đếm số lượng bản ghi hoặc giá trị phi NULL</v>
-      </c>
-      <c r="F5" t="str">
-        <v>SUM() — tính tổng các giá trị số trong cột</v>
       </c>
       <c r="G5" t="str">
         <v>AVG() — tính trung bình cộng các giá trị số</v>
       </c>
       <c r="H5" t="str">
-        <v>TOTAL() — hàm tính tổng số cột hiển thị trong bảng</v>
+        <v>SUM() — tính tổng các giá trị số trong cột</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>GROUP BY gom nhóm các dòng có cùng giá trị trên các cột chỉ định để thực hiện các phép toán gom nhóm (Aggregate) trên từng nhóm đó.</v>
       </c>
       <c r="E6" t="str">
+        <v>Các phép nối bảng như LEFT JOIN, RIGHT JOIN, FULL OUTER JOIN — kết nối dữ liệu nhiều bảng</v>
+      </c>
+      <c r="F6" t="str">
         <v>Các hàm gom nhóm (Aggregate Functions) như SUM, AVG, COUNT, MIN, MAX — thực hiện tính toán trên từng nhóm bản ghi</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v>Các hàm xử lý chuỗi văn bản như CONCAT, SUBSTRING, REPLACE — biến đổi chuỗi</v>
+      </c>
+      <c r="H6" t="str">
         <v>Các câu lệnh điều kiện rẽ nhánh như IF, ELSE, CASE WHEN — xử lý logic hiển thị</v>
       </c>
-      <c r="G6" t="str">
-        <v>Các phép nối bảng như LEFT JOIN, RIGHT JOIN, FULL OUTER JOIN — kết nối dữ liệu nhiều bảng</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Các hàm xử lý chuỗi văn bản như CONCAT, SUBSTRING, REPLACE — biến đổi chuỗi</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>DISTINCT đứng ngay sau SELECT để lọc bỏ các bản ghi trùng lặp hoàn toàn trên tất cả các cột được chọn, trả về các bản ghi độc bản.</v>
       </c>
       <c r="E7" t="str">
-        <v>Loại bỏ các dòng kết quả trùng lặp hoàn toàn khỏi tập kết quả trả về — giữ lại các giá trị duy nhất</v>
+        <v>Liên kết hai bảng dữ liệu có chung khóa chính với nhau — nối bảng dữ liệu</v>
       </c>
       <c r="F7" t="str">
         <v>Sắp xếp kết quả trả về theo thứ tự bảng chữ cái một cách tự động — sắp xếp kết quả</v>
       </c>
       <c r="G7" t="str">
-        <v>Liên kết hai bảng dữ liệu có chung khóa chính với nhau — nối bảng dữ liệu</v>
+        <v>Loại bỏ các dòng kết quả trùng lặp hoàn toàn khỏi tập kết quả trả về — giữ lại các giá trị duy nhất</v>
       </c>
       <c r="H7" t="str">
         <v>Tự động điền các giá trị NULL bằng giá trị mặc định của hệ thống — làm sạch dữ liệu</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>NULL đại diện cho việc thiếu dữ liệu (missing data) hoặc dữ liệu chưa xác định. Nó là trạng thái đặc biệt, không bằng 0 và không bằng chuỗi rỗng.</v>
       </c>
       <c r="E8" t="str">
-        <v>Giá trị trống, chưa xác định hoặc không tồn tại trong ô dữ liệu — không tương đương với số 0 hay chuỗi rỗng</v>
+        <v>Một lỗi cú pháp phát sinh khi người dùng quên nhập dữ liệu trong câu lệnh INSERT</v>
       </c>
       <c r="F8" t="str">
         <v>Số 0 trong các cột định dạng kiểu số nguyên hoặc số thực — giá trị số tối thiểu</v>
       </c>
       <c r="G8" t="str">
+        <v>Giá trị trống, chưa xác định hoặc không tồn tại trong ô dữ liệu — không tương đương với số 0 hay chuỗi rỗng</v>
+      </c>
+      <c r="H8" t="str">
         <v>Một chuỗi ký tự rỗng "" trong các cột kiểu văn bản — giá trị văn bản rỗng</v>
       </c>
-      <c r="H8" t="str">
-        <v>Một lỗi cú pháp phát sinh khi người dùng quên nhập dữ liệu trong câu lệnh INSERT</v>
-      </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>INSERT INTO là lệnh thuộc nhóm DML (Data Manipulation Language) dùng để chèn thêm một hoặc nhiều dòng dữ liệu mới vào bảng.</v>
       </c>
       <c r="E9" t="str">
-        <v>INSERT INTO — thêm các dòng dữ liệu mới vào bảng</v>
+        <v>CREATE TABLE — tạo cấu trúc bảng mới trong database</v>
       </c>
       <c r="F9" t="str">
-        <v>CREATE TABLE — tạo cấu trúc bảng mới trong database</v>
+        <v>ADD ROW — từ khóa khai báo thêm dòng của ngôn ngữ định nghĩa cấu trúc</v>
       </c>
       <c r="G9" t="str">
         <v>UPDATE — sửa đổi dữ liệu hiện có của các dòng trong bảng</v>
       </c>
       <c r="H9" t="str">
-        <v>ADD ROW — từ khóa khai báo thêm dòng của ngôn ngữ định nghĩa cấu trúc</v>
+        <v>INSERT INTO — thêm các dòng dữ liệu mới vào bảng</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>WHERE lọc các bản ghi nguồn (rows) trước khi tính toán gom nhóm. HAVING dùng để lọc các nhóm (groups) thỏa mãn điều kiện trên các hàm aggregate.</v>
       </c>
       <c r="E10" t="str">
+        <v>WHERE chỉ dùng cho kiểu dữ liệu số; HAVING chỉ dùng cho kiểu dữ liệu chuỗi ký tự</v>
+      </c>
+      <c r="F10" t="str">
+        <v>WHERE bắt buộc phải có trong mọi truy vấn; HAVING chỉ dùng khi thực hiện phép nối LEFT JOIN</v>
+      </c>
+      <c r="G10" t="str">
         <v>WHERE lọc dữ liệu trước khi gom nhóm (GROUP BY); HAVING lọc kết quả sau khi đã gom nhóm và tính toán hàm aggregate</v>
       </c>
-      <c r="F10" t="str">
-        <v>WHERE chỉ dùng cho kiểu dữ liệu số; HAVING chỉ dùng cho kiểu dữ liệu chuỗi ký tự</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>WHERE đứng sau mệnh đề GROUP BY; HAVING đứng trước mệnh đề GROUP BY</v>
       </c>
-      <c r="H10" t="str">
-        <v>WHERE bắt buộc phải có trong mọi truy vấn; HAVING chỉ dùng khi thực hiện phép nối LEFT JOIN</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Hàm `ROW_NUMBER() OVER` là Window Function. `PARTITION BY department_id` chia nhân viên thành các nhóm theo phòng ban, và `ORDER BY salary DESC` đánh số thứ tự từ 1 (lương cao nhất) đến hết trong nhóm đó.</v>
       </c>
       <c r="E11" t="str">
-        <v>Đánh số thứ tự tăng dần từ 1 cho nhân viên trong từng phòng ban theo mức lương giảm dần — hàm phân tích cửa sổ (Window Function)</v>
+        <v>Sắp xếp toàn bộ bảng nhân viên theo thứ tự phòng ban tăng dần và lương giảm dần — sắp xếp bảng</v>
       </c>
       <c r="F11" t="str">
         <v>Tính tổng lương của nhân viên trong từng phòng ban một cách tự động — hàm gom nhóm</v>
       </c>
       <c r="G11" t="str">
+        <v>Đánh số thứ tự tăng dần từ 1 cho nhân viên trong từng phòng ban theo mức lương giảm dần — hàm phân tích cửa sổ (Window Function)</v>
+      </c>
+      <c r="H11" t="str">
         <v>Xóa bỏ các nhân viên có lương trùng nhau trong cùng một phòng ban — lọc dữ liệu</v>
       </c>
-      <c r="H11" t="str">
-        <v>Sắp xếp toàn bộ bảng nhân viên theo thứ tự phòng ban tăng dần và lương giảm dần — sắp xếp bảng</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -749,10 +749,10 @@
         <v>Chuyển đổi kiểu dữ liệu của cột column_name thành kiểu số nguyên (Integer)</v>
       </c>
       <c r="G12" t="str">
+        <v>Tự động cộng thêm 0 vào tất cả các giá trị số trong cột column_name</v>
+      </c>
+      <c r="H12" t="str">
         <v>Đếm số lượng giá trị NULL xuất hiện trong cột column_name của bảng dữ liệu</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Tự động cộng thêm 0 vào tất cả các giá trị số trong cột column_name</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -801,19 +801,19 @@
         <v>Hàm aggregate `COUNT(OrderID)` không được phép đặt trong WHERE. Điều kiện lọc số đơn hàng của từng nhóm khách hàng phải được đặt ở mệnh đề HAVING sau GROUP BY.</v>
       </c>
       <c r="E14" t="str">
+        <v>SELECT CustomerID, SUM(OrderID) FROM Orders GROUP BY CustomerID HAVING SUM(OrderID) &gt; 5;</v>
+      </c>
+      <c r="F14" t="str">
         <v>SELECT CustomerID, COUNT(OrderID) FROM Orders GROUP BY CustomerID HAVING COUNT(OrderID) &gt; 5;</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>SELECT CustomerID, COUNT(OrderID) FROM Orders WHERE COUNT(OrderID) &gt; 5 GROUP BY CustomerID;</v>
-      </c>
-      <c r="G14" t="str">
-        <v>SELECT CustomerID, SUM(OrderID) FROM Orders GROUP BY CustomerID HAVING SUM(OrderID) &gt; 5;</v>
       </c>
       <c r="H14" t="str">
         <v>SELECT CustomerID, COUNT(OrderID) FROM Orders GROUP BY CustomerID WHERE COUNT(OrderID) &gt; 5;</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>UNION lọc trùng lặp (duplication removal), do đó tốn tài nguyên sắp xếp/lọc hơn. UNION ALL chỉ ghép nối cơ học tập kết quả nên nhanh hơn.</v>
       </c>
       <c r="E15" t="str">
+        <v>UNION chỉ chạy được trên kiểu dữ liệu số; UNION ALL chạy được trên mọi kiểu dữ liệu</v>
+      </c>
+      <c r="F15" t="str">
+        <v>UNION gộp bảng theo chiều ngang (thêm cột); UNION ALL gộp bảng theo chiều dọc (thêm dòng)</v>
+      </c>
+      <c r="G15" t="str">
         <v>UNION loại bỏ các dòng kết quả trùng lặp; UNION ALL giữ lại toàn bộ các dòng kết quả kể cả dòng trùng lặp</v>
       </c>
-      <c r="F15" t="str">
-        <v>UNION chỉ chạy được trên kiểu dữ liệu số; UNION ALL chạy được trên mọi kiểu dữ liệu</v>
-      </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>UNION ALL thực hiện nhanh hơn UNION vì nó không cần thực hiện thêm bước kiểm tra và lọc trùng lặp — hiệu năng tối ưu hơn</v>
       </c>
-      <c r="H15" t="str">
-        <v>UNION gộp bảng theo chiều ngang (thêm cột); UNION ALL gộp bảng theo chiều dọc (thêm dòng)</v>
-      </c>
       <c r="I15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>CTE định nghĩa các bảng tạm ảo trong phạm vi câu lệnh, giúp phân rã các truy vấn lồng nhau phức tạp thành các khối mã tuần tự, cải thiện độ trực quan.</v>
       </c>
       <c r="E16" t="str">
+        <v>Khi cần kết nối hai database nằm ở hai máy chủ vật lý khác nhau trên mạng</v>
+      </c>
+      <c r="F16" t="str">
         <v>Khi truy vấn phức tạp, lồng nhiều cấp hoặc cần tái sử dụng cùng một tập kết quả trung gian nhiều lần — giúp code rõ ràng, dễ đọc và bảo trì</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Khi cơ sở dữ liệu yêu cầu bắt buộc phải chạy song song nhiều câu lệnh INSERT</v>
       </c>
       <c r="G16" t="str">
         <v>Khi cần tăng tốc độ thực thi của câu lệnh SELECT lên gấp nhiều lần mà không dùng Index</v>
       </c>
       <c r="H16" t="str">
-        <v>Khi cần kết nối hai database nằm ở hai máy chủ vật lý khác nhau trên mạng</v>
+        <v>Khi cơ sở dữ liệu yêu cầu bắt buộc phải chạy song song nhiều câu lệnh INSERT</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -888,10 +888,10 @@
         <v>Index tạo ra một cấu trúc cây tìm kiếm (thường là B-Tree) giúp công cụ tìm dữ liệu nhanh hơn mà không cần quét toàn bộ bảng (Table Scan). Tuy nhiên, mỗi lần ghi dữ liệu, DB phải cập nhật lại cây Index nên làm ghi chậm hơn.</v>
       </c>
       <c r="E17" t="str">
+        <v>Đảm bảo dữ liệu trong cột đó không bao giờ bị ghi đè hoặc chỉnh sửa bởi người dùng</v>
+      </c>
+      <c r="F17" t="str">
         <v>Tăng tốc độ tìm kiếm và truy vấn dữ liệu (SELECT) trên cột đó; làm chậm tốc độ ghi dữ liệu (INSERT/UPDATE/DELETE)</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Đảm bảo dữ liệu trong cột đó không bao giờ bị ghi đè hoặc chỉnh sửa bởi người dùng</v>
       </c>
       <c r="G17" t="str">
         <v>Tự động định dạng lại font chữ và kiểu hiển thị của dữ liệu trong bảng kết quả</v>
@@ -900,7 +900,7 @@
         <v>Tạo ra một bảng sao lưu dự phòng tự động của cột dữ liệu đó để tránh mất mát</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -917,19 +917,19 @@
         <v>Ví dụ với mức lương: 100, 100, 80. RANK() sẽ đánh số: 1, 1, 3 (nhảy qua số 2). DENSE_RANK() đánh số: 1, 1, 2 (đảm bảo số thứ tự liên tục).</v>
       </c>
       <c r="E18" t="str">
+        <v>RANK() trả về tổng số dòng; DENSE_RANK() trả về số dòng duy nhất</v>
+      </c>
+      <c r="F18" t="str">
+        <v>RANK() sắp xếp tăng dần; DENSE_RANK() sắp xếp giảm dần một cách tự động</v>
+      </c>
+      <c r="G18" t="str">
+        <v>RANK() chỉ chạy trên các cột số nguyên; DENSE_RANK() chạy trên mọi kiểu dữ liệu số</v>
+      </c>
+      <c r="H18" t="str">
         <v>RANK() bỏ qua các số thứ tự tiếp theo (tạo khoảng nhảy); DENSE_RANK() đánh số liên tục không tạo khoảng nhảy</v>
       </c>
-      <c r="F18" t="str">
-        <v>RANK() chỉ chạy trên các cột số nguyên; DENSE_RANK() chạy trên mọi kiểu dữ liệu số</v>
-      </c>
-      <c r="G18" t="str">
-        <v>RANK() sắp xếp tăng dần; DENSE_RANK() sắp xếp giảm dần một cách tự động</v>
-      </c>
-      <c r="H18" t="str">
-        <v>RANK() trả về tổng số dòng; DENSE_RANK() trả về số dòng duy nhất</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -952,10 +952,10 @@
         <v>SUM(Amount) OVER (PARTITION BY ProductID) — tính tổng doanh thu của sản phẩm đó cố định cho toàn bộ các dòng</v>
       </c>
       <c r="G19" t="str">
+        <v>SUM(Amount) GROUP BY ProductID — câu lệnh sai cú pháp vì không thể dùng GROUP BY cùng OVER</v>
+      </c>
+      <c r="H19" t="str">
         <v>SUM(Amount) OVER (ORDER BY SaleID) — tính tổng doanh thu lũy kế của toàn bộ cửa hàng không phân chia sản phẩm</v>
-      </c>
-      <c r="H19" t="str">
-        <v>SUM(Amount) GROUP BY ProductID — câu lệnh sai cú pháp vì không thể dùng GROUP BY cùng OVER</v>
       </c>
       <c r="I19">
         <v>1</v>
@@ -978,10 +978,10 @@
         <v>Sử dụng phép so sánh phủ định `!=` hoặc toán tử `OR` trên các cột có chỉ mục, hoặc dùng hàm xử lý chuỗi trên cột trong mệnh đề WHERE (ví dụ: `YEAR(created_date) = 2026`)</v>
       </c>
       <c r="F20" t="str">
+        <v>Sử dụng từ khóa DISTINCT ở đầu câu lệnh SELECT trên một bảng có khóa chính</v>
+      </c>
+      <c r="G20" t="str">
         <v>Sử dụng phép JOIN giữa hai bảng có kích thước dữ liệu chênh lệch nhau quá lớn</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Sử dụng từ khóa DISTINCT ở đầu câu lệnh SELECT trên một bảng có khóa chính</v>
       </c>
       <c r="H20" t="str">
         <v>Đặt tên bảng quá dài hoặc chứa các ký tự đặc biệt như dấu gạch dưới '_'</v>
@@ -1007,13 +1007,13 @@
         <v>FROM → WHERE → GROUP BY → HAVING → SELECT (bao gồm Window Function) → ORDER BY — thứ tự thực thi chuẩn của SQL engine</v>
       </c>
       <c r="F21" t="str">
-        <v>FROM → SELECT → WHERE → GROUP BY → HAVING → ORDER BY — thứ tự thực thi từ trái qua phải của câu lệnh</v>
+        <v>FROM → GROUP BY → HAVING → WHERE → Window Function → SELECT → ORDER BY — thứ tự ưu tiên gom nhóm trước</v>
       </c>
       <c r="G21" t="str">
         <v>WHERE → FROM → GROUP BY → HAVING → SELECT → Window Function → ORDER BY — thứ tự ưu tiên lọc dữ liệu nguồn trước</v>
       </c>
       <c r="H21" t="str">
-        <v>FROM → GROUP BY → HAVING → WHERE → Window Function → SELECT → ORDER BY — thứ tự ưu tiên gom nhóm trước</v>
+        <v>FROM → SELECT → WHERE → GROUP BY → HAVING → ORDER BY — thứ tự thực thi từ trái qua phải của câu lệnh</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -1033,19 +1033,19 @@
         <v>Star Schema tối ưu hóa cho việc đọc và phân tích dữ liệu nhanh trong kho dữ liệu (Data Warehouse). Các bảng chiều (Dim) được phi chuẩn hóa (denormalized) để tránh JOIN nhiều cấp như Snowflake hay 3NF.</v>
       </c>
       <c r="E22" t="str">
+        <v>Mô hình Lược đồ bông tuyết (Snowflake Schema) chuẩn hóa tối đa các bảng Dimension để tránh dư thừa dữ liệu</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Mô hình cơ sở dữ liệu phi quan hệ (NoSQL) dạng Document-based để lưu trữ dữ liệu dưới dạng các file JSON độc lập</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Mô hình chuẩn hóa dạng chuẩn 3 (3NF) để đảm bảo không tồn tại bất kỳ sự dư thừa dữ liệu nào</v>
+      </c>
+      <c r="H22" t="str">
         <v>Mô hình Lược đồ hình sao (Star Schema) gồm các bảng Fact ở giữa kết nối trực tiếp với các bảng Dimension xung quanh — giảm thiểu các phép nối bảng phức tạp</v>
       </c>
-      <c r="F22" t="str">
-        <v>Mô hình Lược đồ bông tuyết (Snowflake Schema) chuẩn hóa tối đa các bảng Dimension để tránh dư thừa dữ liệu</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Mô hình cơ sở dữ liệu phi quan hệ (NoSQL) dạng Document-based để lưu trữ dữ liệu dưới dạng các file JSON độc lập</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Mô hình chuẩn hóa dạng chuẩn 3 (3NF) để đảm bảo không tồn tại bất kỳ sự dư thừa dữ liệu nào</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1068,10 +1068,10 @@
         <v>Self-Join Subquery (tự nối) — kết nối bảng Orders với chính nó để lọc các bản ghi trùng lặp</v>
       </c>
       <c r="G23" t="str">
+        <v>Recursive Subquery (đệ quy) — truy vấn lặp đi lặp lại nhiều lần cho đến khi bảng Customers không còn dữ liệu</v>
+      </c>
+      <c r="H23" t="str">
         <v>Independent Subquery (truy vấn con độc lập) — chỉ chạy duy nhất một lần để lấy danh sách khách hàng Việt Nam trước khi chạy câu lệnh ngoài</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Recursive Subquery (đệ quy) — truy vấn lặp đi lặp lại nhiều lần cho đến khi bảng Customers không còn dữ liệu</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1091,19 +1091,19 @@
         <v>TRUNCATE là lệnh DDL, nó không kích hoạt các trigger DELETE, giải phóng không gian lưu trữ trực tiếp và chỉ ghi log ở mức page deallocation nên không thể rollback từng dòng độc lập và chạy cực nhanh.</v>
       </c>
       <c r="E24" t="str">
+        <v>TRUNCATE xóa cấu trúc bảng; DELETE xóa dữ liệu và giữ lại cấu trúc bảng rỗng</v>
+      </c>
+      <c r="F24" t="str">
+        <v>TRUNCATE có thể khôi phục lại dữ liệu bằng lệnh ROLLBACK; DELETE không thể khôi phục lại dữ liệu</v>
+      </c>
+      <c r="G24" t="str">
         <v>TRUNCATE xóa toàn bộ dòng dữ liệu bằng cách giải phóng các data blocks và không ghi log chi tiết cho từng dòng (DDL) nên cực nhanh; DELETE xóa từng dòng dữ liệu và ghi log rollback (DML) nên chậm hơn</v>
-      </c>
-      <c r="F24" t="str">
-        <v>TRUNCATE xóa cấu trúc bảng; DELETE xóa dữ liệu và giữ lại cấu trúc bảng rỗng</v>
-      </c>
-      <c r="G24" t="str">
-        <v>TRUNCATE có thể khôi phục lại dữ liệu bằng lệnh ROLLBACK; DELETE không thể khôi phục lại dữ liệu</v>
       </c>
       <c r="H24" t="str">
         <v>TRUNCATE chỉ chạy được khi bảng không có dữ liệu; DELETE chạy được trên mọi bảng</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Khi giao dịch (Fact) xuất hiện nhưng thông tin khách hàng (Dim) chưa được tạo ở kho dữ liệu, để tránh lỗi khóa ngoại hoặc mất giao dịch, ta tạo một bản ghi Dim rỗng tạm thời để liên kết, tránh gián đoạn luồng ETL.</v>
       </c>
       <c r="E25" t="str">
+        <v>Dữ liệu kiểu Date/Time bị sai múi giờ giữa hệ thống nguồn và đích. Giải pháp: Sử dụng hàm CONVERT múi giờ sang UTC</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Cơ sở dữ liệu bị quá tải khiến các câu lệnh JOIN bị chạy chậm hơn bình thường. Giải pháp: Tăng kích thước bộ nhớ RAM của máy chủ</v>
+      </c>
+      <c r="G25" t="str">
         <v>Dữ liệu Fact (giao dịch) đến kho dữ liệu trước khi dữ liệu Dimension (thông tin đối tượng liên quan) được cập nhật. Giải pháp: Tạo bản ghi Dimension tạm thời (placeholder/dummy record) với các thông tin mặc định, sau đó cập nhật lại khi dữ liệu thật đến</v>
       </c>
-      <c r="F25" t="str">
+      <c r="H25" t="str">
         <v>Dữ liệu Dimension đến trễ hơn so với lịch trình hàng ngày của hệ thống. Giải pháp: Hủy bỏ toàn bộ các giao dịch phát sinh trong ngày hôm đó</v>
       </c>
-      <c r="G25" t="str">
-        <v>Cơ sở dữ liệu bị quá tải khiến các câu lệnh JOIN bị chạy chậm hơn bình thường. Giải pháp: Tăng kích thước bộ nhớ RAM của máy chủ</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Dữ liệu kiểu Date/Time bị sai múi giờ giữa hệ thống nguồn và đích. Giải pháp: Sử dụng hàm CONVERT múi giờ sang UTC</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Xóa một lượng lớn dữ liệu bằng một lệnh DELETE đơn lẻ sẽ chiếm dụng khóa lớn và ghi log khổng lồ gây treo DB. Việc xóa theo lô (batching) hoặc sử dụng Partitioning (DROP Partition là DDL cực nhanh) là giải pháp tối ưu cho dữ liệu lớn.</v>
       </c>
       <c r="E26" t="str">
+        <v>Chạy một câu lệnh `DELETE FROM Logs WHERE log_date &lt; DATE_SUB(NOW(), INTERVAL 3 YEAR);` vào giờ cao điểm</v>
+      </c>
+      <c r="F26" t="str">
         <v>Chia nhỏ dữ liệu cần xóa thành các lô nhỏ (chunking/batching) sử dụng vòng lặp kết hợp LIMIT trong giao dịch để xóa dần dần, hoặc sử dụng phân vùng bảng (Partitioning) để DROP phân vùng cũ trực tiếp</v>
       </c>
-      <c r="F26" t="str">
-        <v>Chạy một câu lệnh `DELETE FROM Logs WHERE log_date &lt; DATE_SUB(NOW(), INTERVAL 3 YEAR);` vào giờ cao điểm</v>
-      </c>
       <c r="G26" t="str">
+        <v>Tắt hoàn toàn cơ sở dữ liệu trong vòng 1 ngày để thực hiện việc dọn dẹp dữ liệu cũ</v>
+      </c>
+      <c r="H26" t="str">
         <v>Tạo một bảng mới, copy toàn bộ dữ liệu log mới sang bảng đó rồi dùng DROP TABLE bảng Logs cũ ngay lập tức</v>
       </c>
-      <c r="H26" t="str">
-        <v>Tắt hoàn toàn cơ sở dữ liệu trong vòng 1 ngày để thực hiện việc dọn dẹp dữ liệu cũ</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
